--- a/data/trans_dic/P3A$otraSIcobra-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,75</t>
+          <t>0,67; 7,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,65</t>
+          <t>0,39; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,8</t>
+          <t>0,93; 4,68</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,07</t>
+          <t>0,18; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,22</t>
+          <t>0,11; 1,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,97</t>
+          <t>0,64; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,73</t>
+          <t>0,44; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,86</t>
+          <t>0,65; 2,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,49</t>
+          <t>0,47; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,47</t>
+          <t>1,51; 3,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,5</t>
+          <t>1,01; 2,6</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,26</t>
+          <t>0,96; 3,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,35</t>
+          <t>1,29; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,82</t>
+          <t>1,38; 2,74</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,63</t>
+          <t>3,71; 7,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,75</t>
+          <t>1,2; 5,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,73</t>
+          <t>2,09; 5,78</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 15,5</t>
+          <t>9,3; 15,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,82</t>
+          <t>11,98; 17,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,49</t>
+          <t>11,58; 15,44</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,43</t>
+          <t>2,11; 3,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,84</t>
+          <t>2,68; 3,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,5</t>
+          <t>2,6; 3,53</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2702; 27008</t>
+          <t>2670; 29090</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1217; 11431</t>
+          <t>1221; 12634</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6792; 34250</t>
+          <t>6649; 33408</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>976; 10597</t>
+          <t>947; 10336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1014; 11450</t>
+          <t>1027; 11236</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3492; 15924</t>
+          <t>3442; 15673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2539; 10233</t>
+          <t>2599; 11372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7188; 20961</t>
+          <t>7372; 22746</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4014; 22088</t>
+          <t>4137; 22163</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10873; 24728</t>
+          <t>10758; 24232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16803; 39939</t>
+          <t>16207; 41542</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5435; 18291</t>
+          <t>5363; 18186</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7670; 18352</t>
+          <t>7088; 18659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15273; 31281</t>
+          <t>15357; 30441</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13387; 28018</t>
+          <t>13627; 27234</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7310; 34979</t>
+          <t>7310; 35011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20975; 55854</t>
+          <t>20359; 56376</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27021; 43826</t>
+          <t>26307; 42804</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51034; 71612</t>
+          <t>51000; 72842</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82626; 109741</t>
+          <t>82039; 109375</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>71217; 118540</t>
+          <t>72969; 117979</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>101413; 142650</t>
+          <t>99331; 143985</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>187029; 251003</t>
+          <t>186252; 253087</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobra-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,27</t>
+          <t>0,7; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,03</t>
+          <t>0,32; 3,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,68</t>
+          <t>0,9; 4,39</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,02</t>
+          <t>0,21; 2,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,92</t>
+          <t>0,65; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,92</t>
+          <t>0,57; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,02</t>
+          <t>0,74; 1,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,5</t>
+          <t>1,03; 3,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,4</t>
+          <t>1,57; 3,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,6</t>
+          <t>1,5; 2,97</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,24</t>
+          <t>0,96; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,41</t>
+          <t>1,27; 3,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,74</t>
+          <t>1,3; 2,69</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,42</t>
+          <t>3,71; 7,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,76</t>
+          <t>4,16; 7,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,78</t>
+          <t>4,26; 6,85</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,3; 15,14</t>
+          <t>9,47; 15,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,11</t>
+          <t>12,13; 17,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,44</t>
+          <t>11,85; 15,68</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,41</t>
+          <t>2,43; 3,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,88</t>
+          <t>3,16; 4,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,53</t>
+          <t>2,96; 3,69</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15787</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2670; 29090</t>
+          <t>2847; 29230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1221; 12634</t>
+          <t>1163; 12264</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6649; 33408</t>
+          <t>6907; 33855</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>947; 10336</t>
+          <t>1076; 11204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1027; 11236</t>
+          <t>1075; 11724</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>15496</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3442; 15673</t>
+          <t>4033; 16740</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2599; 11372</t>
+          <t>3536; 12253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7372; 22746</t>
+          <t>9223; 24339</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>31160</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4137; 22163</t>
+          <t>7220; 24249</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10758; 24232</t>
+          <t>11575; 24321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16207; 41542</t>
+          <t>21552; 42618</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>23172</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5363; 18186</t>
+          <t>5877; 18078</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7088; 18659</t>
+          <t>7711; 18543</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15357; 30441</t>
+          <t>15880; 32785</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>46278</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13627; 27234</t>
+          <t>15051; 30592</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7310; 35011</t>
+          <t>18224; 32504</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20359; 56376</t>
+          <t>35946; 57855</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>37343</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95047</t>
+          <t>105911</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26307; 42804</t>
+          <t>29364; 47914</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51000; 72842</t>
+          <t>56373; 81396</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82039; 109375</t>
+          <t>91843; 121495</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>72969; 117979</t>
+          <t>85939; 127884</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>99331; 143985</t>
+          <t>118070; 156332</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>186252; 253087</t>
+          <t>215168; 268184</t>
         </is>
       </c>
     </row>
